--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487025_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487025_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.4936</v>
+        <v>8.3188</v>
       </c>
       <c r="E2" t="n">
-        <v>5.8063</v>
+        <v>6.6316</v>
       </c>
       <c r="F2" t="n">
         <v>1.6873</v>
@@ -610,10 +610,10 @@
         <v>2.8748</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9377</v>
+        <v>-0.1124</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.178</v>
+        <v>-0.3527</v>
       </c>
       <c r="U2" t="n">
         <v>0.2403</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7362</v>
+        <v>3.2428</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6653</v>
+        <v>1.1423</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0708</v>
+        <v>2.1005</v>
       </c>
       <c r="G3" t="n">
         <v>1.9188</v>
@@ -688,13 +688,13 @@
         <v>2.8748</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0307</v>
+        <v>-0.524</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0545</v>
+        <v>-0.5775</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0238</v>
+        <v>0.0535</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0145</v>
+        <v>2.9653</v>
       </c>
       <c r="E4" t="n">
-        <v>0.121</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8935</v>
+        <v>2.36</v>
       </c>
       <c r="G4" t="n">
         <v>3.3855</v>
@@ -766,13 +766,13 @@
         <v>1.6427</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3457</v>
+        <v>0.2964</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6201</v>
+        <v>-0.1358</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9658</v>
+        <v>0.4322</v>
       </c>
       <c r="V4" t="n">
         <v>0.7207</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9504</v>
+        <v>2.7904</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0669</v>
+        <v>0.4174</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0173</v>
+        <v>2.373</v>
       </c>
       <c r="G5" t="n">
         <v>-1.12</v>
@@ -844,13 +844,13 @@
         <v>2.8748</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.5723</v>
+        <v>-0.7323</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0153</v>
+        <v>-0.531</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5570000000000001</v>
+        <v>-0.2013</v>
       </c>
       <c r="V5" t="n">
         <v>1.7679</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4814</v>
+        <v>0.2704</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2999</v>
+        <v>-0.7183</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7812</v>
+        <v>0.9887</v>
       </c>
       <c r="G6" t="n">
         <v>-0.0055</v>
@@ -922,13 +922,13 @@
         <v>1.2321</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5218</v>
+        <v>0.3109</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5461</v>
+        <v>0.1277</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0243</v>
+        <v>0.1832</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2402</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4669</v>
+        <v>-0.299</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.8288</v>
+        <v>-1.6312</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3619</v>
+        <v>1.3322</v>
       </c>
       <c r="G7" t="n">
         <v>-1.9392</v>
@@ -1000,13 +1000,13 @@
         <v>2.2588</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3491</v>
+        <v>-0.1811</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3566</v>
+        <v>-0.159</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0075</v>
+        <v>-0.0222</v>
       </c>
       <c r="V7" t="n">
         <v>0.5893</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.778</v>
+        <v>-0.5852000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4086</v>
+        <v>-1.0676</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6306</v>
+        <v>0.4824</v>
       </c>
       <c r="G8" t="n">
         <v>0.2864</v>
@@ -1078,13 +1078,13 @@
         <v>1.8481</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3196</v>
+        <v>0.5123</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1513</v>
+        <v>0.1897</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4709</v>
+        <v>0.3226</v>
       </c>
       <c r="V8" t="n">
         <v>-1.1786</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.399</v>
+        <v>-1.4328</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0723</v>
+        <v>-1.2544</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3267</v>
+        <v>-0.1785</v>
       </c>
       <c r="G9" t="n">
         <v>-1.629</v>
@@ -1156,13 +1156,13 @@
         <v>0.616</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2033</v>
+        <v>0.1695</v>
       </c>
       <c r="T9" t="n">
-        <v>0.244</v>
+        <v>0.0619</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0407</v>
+        <v>0.1075</v>
       </c>
       <c r="V9" t="n">
         <v>-0.5893</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0266</v>
+        <v>-1.9475</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.321</v>
+        <v>-3.1233</v>
       </c>
       <c r="F10" t="n">
-        <v>1.2944</v>
+        <v>1.1758</v>
       </c>
       <c r="G10" t="n">
         <v>-3.5127</v>
@@ -1234,13 +1234,13 @@
         <v>2.8748</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1217</v>
+        <v>-0.0427</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3489</v>
+        <v>-0.1513</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2271</v>
+        <v>0.1086</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2402</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.4241</v>
+        <v>-5.7536</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.077</v>
+        <v>-3.4955</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.3471</v>
+        <v>-2.2582</v>
       </c>
       <c r="G11" t="n">
         <v>-3.8971</v>
@@ -1312,13 +1312,13 @@
         <v>0.4107</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4196</v>
+        <v>0.0901</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4725</v>
+        <v>0.0541</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0529</v>
+        <v>0.036</v>
       </c>
       <c r="V11" t="n">
         <v>-2.3573</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.581500000000001</v>
+        <v>7.5696</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.4819</v>
+        <v>-2.4937</v>
       </c>
       <c r="F12" t="n">
         <v>10.0632</v>
@@ -1390,13 +1390,13 @@
         <v>19.5076</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2015</v>
+        <v>-0.2133</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.4621</v>
+        <v>-1.4739</v>
       </c>
       <c r="U12" t="n">
-        <v>1.2605</v>
+        <v>1.2604</v>
       </c>
       <c r="V12" t="n">
         <v>0.2401999999999997</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.0461</v>
+        <v>5.1368</v>
       </c>
       <c r="E13" t="n">
-        <v>1.6291</v>
+        <v>1.8383</v>
       </c>
       <c r="F13" t="n">
-        <v>3.417</v>
+        <v>3.2985</v>
       </c>
       <c r="G13" t="n">
         <v>3.955</v>
@@ -1468,13 +1468,13 @@
         <v>1.2321</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0295</v>
+        <v>0.1202</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5542</v>
+        <v>-0.345</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5837</v>
+        <v>0.4652</v>
       </c>
       <c r="V13" t="n">
         <v>-0.1704</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.3526</v>
+        <v>2.2697</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4754</v>
+        <v>3.3122</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.1228</v>
+        <v>-1.0426</v>
       </c>
       <c r="G14" t="n">
         <v>5.2233</v>
@@ -1546,13 +1546,13 @@
         <v>1.6427</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.039</v>
+        <v>-0.122</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.3174</v>
+        <v>-0.4806</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2784</v>
+        <v>0.3586</v>
       </c>
       <c r="V14" t="n">
         <v>0.6591</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5604</v>
+        <v>0.7086</v>
       </c>
       <c r="E15" t="n">
         <v>-0.7966</v>
       </c>
       <c r="F15" t="n">
-        <v>1.357</v>
+        <v>1.5052</v>
       </c>
       <c r="G15" t="n">
         <v>0.4616</v>
@@ -1624,13 +1624,13 @@
         <v>0.2053</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1065</v>
+        <v>0.0417</v>
       </c>
       <c r="T15" t="n">
         <v>-0.1976</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0911</v>
+        <v>0.2393</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3249</v>
+        <v>0.623</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0258</v>
+        <v>1.235</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7009</v>
+        <v>-0.612</v>
       </c>
       <c r="G16" t="n">
         <v>1.192</v>
@@ -1702,13 +1702,13 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2778</v>
+        <v>0.0203</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1976</v>
+        <v>0.0116</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.08019999999999999</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="V16" t="n">
         <v>-0.5893</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3529</v>
+        <v>-0.1297</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.0128</v>
+        <v>-1.9082</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6599</v>
+        <v>1.7785</v>
       </c>
       <c r="G17" t="n">
         <v>0.8663</v>
@@ -1780,13 +1780,13 @@
         <v>1.4374</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.08359999999999999</v>
+        <v>0.1396</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0931</v>
+        <v>0.0115</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0095</v>
+        <v>0.1281</v>
       </c>
       <c r="V17" t="n">
         <v>-0.5195</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. HENDERSON</t>
+          <t>J. PARRA BAEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7964</v>
+        <v>-1.1247</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3868</v>
+        <v>-3.817</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.1831</v>
+        <v>2.6923</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.8874</v>
+        <v>-1.731</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1752</v>
+        <v>-0.8597</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.0626</v>
+        <v>-0.8713</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6508</v>
+        <v>-2.7715</v>
       </c>
       <c r="K18" t="n">
-        <v>1.2298</v>
+        <v>-1.0604</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.579</v>
+        <v>-1.7112</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.5382</v>
+        <v>1.0405</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.0546</v>
+        <v>0.2007</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.4836</v>
+        <v>0.8399</v>
       </c>
       <c r="P18" t="n">
-        <v>0.8214</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R18" t="n">
-        <v>0.8214</v>
+        <v>1.6427</v>
       </c>
       <c r="S18" t="n">
-        <v>1.4483</v>
+        <v>-0.4717</v>
       </c>
       <c r="T18" t="n">
-        <v>0.736</v>
+        <v>-0.4109</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7123</v>
+        <v>-0.0608</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.1786</v>
+        <v>1.4887</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.4189</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.1786</v>
+        <v>0.0698</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. ABDULSALAM</t>
+          <t>A. MONTERO ISLA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9343</v>
+        <v>-1.3794</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.4831</v>
+        <v>-1.973</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5489</v>
+        <v>0.5936</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3637</v>
+        <v>-0.7613</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.535</v>
+        <v>0.0227</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1713</v>
+        <v>-0.784</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.8487</v>
+        <v>0.2665</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.9012</v>
+        <v>0.2404</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0525</v>
+        <v>0.0261</v>
       </c>
       <c r="M19" t="n">
-        <v>0.485</v>
+        <v>-1.0278</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3662</v>
+        <v>-0.2177</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1188</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="P19" t="n">
-        <v>-5.3389</v>
+        <v>-1.4374</v>
       </c>
       <c r="Q19" t="n">
-        <v>-6.1603</v>
+        <v>-2.0534</v>
       </c>
       <c r="R19" t="n">
-        <v>0.8214</v>
+        <v>0.616</v>
       </c>
       <c r="S19" t="n">
-        <v>4.2879</v>
+        <v>-0.1191</v>
       </c>
       <c r="T19" t="n">
-        <v>2.6963</v>
+        <v>-0.4263</v>
       </c>
       <c r="U19" t="n">
-        <v>1.5916</v>
+        <v>0.3072</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5195</v>
+        <v>0.9384</v>
       </c>
       <c r="W19" t="n">
-        <v>0.8295</v>
+        <v>0.2402</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.349</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. PARRA BAEZ</t>
+          <t>C. HENDERSON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0157</v>
+        <v>-1.6402</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.0262</v>
+        <v>0.7592</v>
       </c>
       <c r="F20" t="n">
-        <v>2.0105</v>
+        <v>-2.3994</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.731</v>
+        <v>-1.8874</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.8597</v>
+        <v>0.1752</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8713</v>
+        <v>-2.0626</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.7715</v>
+        <v>0.6508</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.0604</v>
+        <v>1.2298</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.7112</v>
+        <v>-0.579</v>
       </c>
       <c r="M20" t="n">
-        <v>1.0405</v>
+        <v>-2.5382</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2007</v>
+        <v>-1.0546</v>
       </c>
       <c r="O20" t="n">
-        <v>0.8399</v>
+        <v>-1.4836</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.4107</v>
+        <v>0.8214</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6427</v>
+        <v>0.8214</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.3627</v>
+        <v>0.6044</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6201</v>
+        <v>0.1084</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7426</v>
+        <v>0.4961</v>
       </c>
       <c r="V20" t="n">
-        <v>1.4887</v>
+        <v>-1.1786</v>
       </c>
       <c r="W20" t="n">
-        <v>1.4189</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.0698</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. MONTERO ISLA</t>
+          <t>J. NVE MALEVA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.7097</v>
+        <v>-2.7658</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.6006</v>
+        <v>-0.8315</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1091</v>
+        <v>-1.9343</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.7613</v>
+        <v>-2.9882</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0227</v>
+        <v>-1.8781</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.784</v>
+        <v>-1.11</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2665</v>
+        <v>-0.5366</v>
       </c>
       <c r="K21" t="n">
-        <v>0.2404</v>
+        <v>-0.655</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0261</v>
+        <v>0.1184</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.0278</v>
+        <v>-2.4516</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2177</v>
+        <v>-1.2231</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.2284</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.4374</v>
+        <v>0.616</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0.616</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4494</v>
+        <v>-0.0445</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.054</v>
+        <v>-0.186</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3955</v>
+        <v>0.1415</v>
       </c>
       <c r="V21" t="n">
-        <v>0.9384</v>
+        <v>-0.3491</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2402</v>
+        <v>-0.1088</v>
       </c>
       <c r="X21" t="n">
-        <v>0.6982</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.0016</v>
+        <v>-2.7872</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.6205</v>
+        <v>-2.5159</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3812</v>
+        <v>-0.2713</v>
       </c>
       <c r="G22" t="n">
         <v>-1.2424</v>
@@ -2170,13 +2170,13 @@
         <v>0.2053</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0888</v>
+        <v>0.3032</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2635</v>
+        <v>-0.1589</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3523</v>
+        <v>0.4621</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. NVE MALEVA</t>
+          <t>M. ABDULSALAM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.0551</v>
+        <v>-4.7953</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.0407</v>
+        <v>-5.366</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.0145</v>
+        <v>0.5707</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.9882</v>
+        <v>-0.3637</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.8781</v>
+        <v>-0.535</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.11</v>
+        <v>0.1713</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5366</v>
+        <v>-0.8487</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.655</v>
+        <v>-0.9012</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1184</v>
+        <v>0.0525</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.4516</v>
+        <v>0.485</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.2231</v>
+        <v>0.3662</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.2284</v>
+        <v>0.1188</v>
       </c>
       <c r="P23" t="n">
-        <v>0.616</v>
+        <v>-5.3389</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-6.1603</v>
       </c>
       <c r="R23" t="n">
-        <v>0.616</v>
+        <v>0.8214</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3339</v>
+        <v>1.4268</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3952</v>
+        <v>0.8134</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0613</v>
+        <v>0.6133999999999999</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.3491</v>
+        <v>-0.5195</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.1088</v>
+        <v>0.8295</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.2402</v>
+        <v>-1.349</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.5817</v>
+        <v>-5.884200000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-10.0634</v>
+        <v>-10.0635</v>
       </c>
       <c r="F24" t="n">
-        <v>3.4817</v>
+        <v>4.1792</v>
       </c>
       <c r="G24" t="n">
         <v>2.724200000000001</v>
@@ -2296,7 +2296,7 @@
         <v>0.2758999999999998</v>
       </c>
       <c r="I24" t="n">
-        <v>2.4483</v>
+        <v>2.448299999999999</v>
       </c>
       <c r="J24" t="n">
         <v>6.556899999999999</v>
@@ -2305,7 +2305,7 @@
         <v>2.0471</v>
       </c>
       <c r="L24" t="n">
-        <v>4.509799999999999</v>
+        <v>4.5098</v>
       </c>
       <c r="M24" t="n">
         <v>-3.8326</v>
@@ -2326,16 +2326,16 @@
         <v>9.2403</v>
       </c>
       <c r="S24" t="n">
-        <v>1.2016</v>
+        <v>1.8989</v>
       </c>
       <c r="T24" t="n">
         <v>-1.2604</v>
       </c>
       <c r="U24" t="n">
-        <v>2.4619</v>
+        <v>3.1594</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.2402000000000002</v>
+        <v>-0.2402000000000001</v>
       </c>
       <c r="W24" t="n">
         <v>4.1477</v>
